--- a/output/yearly_benthic_cover_iteration_81_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_81_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.84672959311069</v>
+        <v>45.69807327597362</v>
       </c>
       <c r="M2" t="n">
-        <v>98.73435504681311</v>
+        <v>98.50980771164416</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.88852373563229</v>
+        <v>88.0244074353771</v>
       </c>
       <c r="C3" t="n">
-        <v>45.85953558280089</v>
+        <v>45.933316649852</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228426605206752</v>
+        <v>2.2287196581641</v>
       </c>
       <c r="E3" t="n">
-        <v>5.65928651675613</v>
+        <v>5.708808350546555</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428088684022507</v>
+        <v>0.7429065527213669</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95056517427622</v>
+        <v>33.97476784781862</v>
       </c>
       <c r="H3" t="n">
-        <v>34.16920794650353</v>
+        <v>34.17370142518287</v>
       </c>
       <c r="I3" t="n">
-        <v>6.495673196973349</v>
+        <v>6.552337646435045</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642555427514067</v>
+        <v>4.643165954508542</v>
       </c>
       <c r="K3" t="n">
-        <v>12.1114762643677</v>
+        <v>11.9755925646229</v>
       </c>
       <c r="L3" t="n">
-        <v>48.79579498661103</v>
+        <v>48.85589430857267</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7668068337796</v>
+        <v>106.7648035230476</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.70914137398918</v>
+        <v>87.13690795412815</v>
       </c>
       <c r="C4" t="n">
-        <v>42.30388163591121</v>
+        <v>42.67774982333991</v>
       </c>
       <c r="D4" t="n">
-        <v>2.170125192100433</v>
+        <v>2.186092422367552</v>
       </c>
       <c r="E4" t="n">
-        <v>6.415283031710703</v>
+        <v>6.511571534488525</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7443578224621842</v>
+        <v>0.7444615652920431</v>
       </c>
       <c r="G4" t="n">
-        <v>33.06233043466503</v>
+        <v>33.32495510224661</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24045983326047</v>
+        <v>34.24523200343398</v>
       </c>
       <c r="I4" t="n">
-        <v>5.424348669401721</v>
+        <v>5.471710543224197</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652236390388651</v>
+        <v>4.652884783075269</v>
       </c>
       <c r="K4" t="n">
-        <v>13.29085862601081</v>
+        <v>12.86309204587184</v>
       </c>
       <c r="L4" t="n">
-        <v>44.22482437149539</v>
+        <v>44.27714875172061</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81956463341741</v>
+        <v>99.81799062093236</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.30635200622085</v>
+        <v>86.0256563479786</v>
       </c>
       <c r="C5" t="n">
-        <v>41.74268887280914</v>
+        <v>42.41578881591516</v>
       </c>
       <c r="D5" t="n">
-        <v>2.100741034651515</v>
+        <v>2.132050061308528</v>
       </c>
       <c r="E5" t="n">
-        <v>6.964885708414516</v>
+        <v>7.111903950431668</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7456749057963928</v>
+        <v>0.745779223888684</v>
       </c>
       <c r="G5" t="n">
-        <v>32.00524766872255</v>
+        <v>32.50112934013133</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30104566663406</v>
+        <v>34.30584429887946</v>
       </c>
       <c r="I5" t="n">
-        <v>4.528288860774356</v>
+        <v>4.567829324034644</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660468161227454</v>
+        <v>4.661120149304275</v>
       </c>
       <c r="K5" t="n">
-        <v>14.69364799377915</v>
+        <v>13.97434365202142</v>
       </c>
       <c r="L5" t="n">
-        <v>43.41298678148389</v>
+        <v>43.4578755725294</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84932364807217</v>
+        <v>99.84800804046598</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>83.66787665881668</v>
+        <v>84.65612676925224</v>
       </c>
       <c r="C6" t="n">
-        <v>40.80700297862168</v>
+        <v>41.75575373648312</v>
       </c>
       <c r="D6" t="n">
-        <v>2.019971197674411</v>
+        <v>2.065199323396653</v>
       </c>
       <c r="E6" t="n">
-        <v>7.32697393385269</v>
+        <v>7.524282222037945</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7467976370431455</v>
+        <v>0.7468986892760759</v>
       </c>
       <c r="G6" t="n">
-        <v>30.77470159285015</v>
+        <v>31.48205173084501</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35269130398468</v>
+        <v>34.35733970669948</v>
       </c>
       <c r="I6" t="n">
-        <v>3.779255761891928</v>
+        <v>3.812238289021594</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667485231519659</v>
+        <v>4.668116807975474</v>
       </c>
       <c r="K6" t="n">
-        <v>16.33212334118334</v>
+        <v>15.34387323074777</v>
       </c>
       <c r="L6" t="n">
-        <v>42.73508787850681</v>
+        <v>42.77348888487927</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87421419831183</v>
+        <v>99.87311585211016</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>81.86432484536364</v>
+        <v>83.09577970689041</v>
       </c>
       <c r="C7" t="n">
-        <v>39.58978918156348</v>
+        <v>40.78756244333577</v>
       </c>
       <c r="D7" t="n">
-        <v>1.931646334737665</v>
+        <v>1.98927550498178</v>
       </c>
       <c r="E7" t="n">
-        <v>7.532166716987075</v>
+        <v>7.777816927520489</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7477565281966272</v>
+        <v>0.7478517357456563</v>
       </c>
       <c r="G7" t="n">
-        <v>29.42905304932777</v>
+        <v>30.32466340911678</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39680029704485</v>
+        <v>34.40117984430018</v>
       </c>
       <c r="I7" t="n">
-        <v>3.153423617840733</v>
+        <v>3.180918936815182</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673478301228919</v>
+        <v>4.674073348410352</v>
       </c>
       <c r="K7" t="n">
-        <v>18.13567515463635</v>
+        <v>16.90422029310957</v>
       </c>
       <c r="L7" t="n">
-        <v>42.16955633708095</v>
+        <v>42.20232175552628</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89502067328078</v>
+        <v>99.89410449197163</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>86.80745248917805</v>
+        <v>88.05341803707684</v>
       </c>
       <c r="C8" t="n">
-        <v>41.88940820318775</v>
+        <v>43.09547587932384</v>
       </c>
       <c r="D8" t="n">
-        <v>1.93585305512027</v>
+        <v>1.993571857100984</v>
       </c>
       <c r="E8" t="n">
-        <v>9.366106193487859</v>
+        <v>9.618732084715843</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7493849850066662</v>
+        <v>0.7494669139256893</v>
       </c>
       <c r="G8" t="n">
-        <v>29.92929031061406</v>
+        <v>30.82678078843065</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47170931030664</v>
+        <v>34.4754780405817</v>
       </c>
       <c r="I8" t="n">
-        <v>5.671452478350903</v>
+        <v>5.70522014028642</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683656156291662</v>
+        <v>4.684168212035559</v>
       </c>
       <c r="K8" t="n">
-        <v>13.19254751082194</v>
+        <v>11.94658196292316</v>
       </c>
       <c r="L8" t="n">
-        <v>44.72940668316074</v>
+        <v>44.76817799759034</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81136239717043</v>
+        <v>99.81023583983735</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84.44841249520509</v>
+        <v>86.01535681991375</v>
       </c>
       <c r="C9" t="n">
-        <v>40.40929628336017</v>
+        <v>41.94288211316096</v>
       </c>
       <c r="D9" t="n">
-        <v>1.828504616963995</v>
+        <v>1.901337234896918</v>
       </c>
       <c r="E9" t="n">
-        <v>9.635903499378999</v>
+        <v>9.967566014410826</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507855918254248</v>
+        <v>0.7508503123490543</v>
       </c>
       <c r="G9" t="n">
-        <v>28.2696278886796</v>
+        <v>29.40054853617407</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53613722396953</v>
+        <v>34.53911436805649</v>
       </c>
       <c r="I9" t="n">
-        <v>4.735043725478631</v>
+        <v>4.763125901844809</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692409948908904</v>
+        <v>4.692814452181589</v>
       </c>
       <c r="K9" t="n">
-        <v>15.55158750479492</v>
+        <v>13.98464318008625</v>
       </c>
       <c r="L9" t="n">
-        <v>43.88157586522405</v>
+        <v>43.91399636952261</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84245965337914</v>
+        <v>99.84152166276982</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>81.97996506560384</v>
+        <v>83.86717572872587</v>
       </c>
       <c r="C10" t="n">
-        <v>38.67401912911879</v>
+        <v>40.53366627078812</v>
       </c>
       <c r="D10" t="n">
-        <v>1.717665958128546</v>
+        <v>1.805215654913886</v>
       </c>
       <c r="E10" t="n">
-        <v>9.710504697859578</v>
+        <v>10.12624902976471</v>
       </c>
       <c r="F10" t="n">
-        <v>0.751992091022229</v>
+        <v>0.7520367272510783</v>
       </c>
       <c r="G10" t="n">
-        <v>26.556004848361</v>
+        <v>27.91421190646089</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59163618702252</v>
+        <v>34.59368945354959</v>
       </c>
       <c r="I10" t="n">
-        <v>3.952210714321031</v>
+        <v>3.975543411466494</v>
       </c>
       <c r="J10" t="n">
-        <v>4.69995056888893</v>
+        <v>4.700229545319239</v>
       </c>
       <c r="K10" t="n">
-        <v>18.02003493439618</v>
+        <v>16.13282427127411</v>
       </c>
       <c r="L10" t="n">
-        <v>43.17441694411063</v>
+        <v>43.20120040510875</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86847100762559</v>
+        <v>99.86769094717098</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>79.44607178261677</v>
+        <v>81.66444930913028</v>
       </c>
       <c r="C11" t="n">
-        <v>36.75119246715111</v>
+        <v>38.94714570594309</v>
       </c>
       <c r="D11" t="n">
-        <v>1.605300172633282</v>
+        <v>1.707730031246004</v>
       </c>
       <c r="E11" t="n">
-        <v>9.624943384307171</v>
+        <v>10.13231574788305</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530326794354756</v>
+        <v>0.7530550552617313</v>
       </c>
       <c r="G11" t="n">
-        <v>24.81877163937706</v>
+        <v>26.40678294666243</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63950325403187</v>
+        <v>34.64053254203962</v>
       </c>
       <c r="I11" t="n">
-        <v>3.29806640636019</v>
+        <v>3.317438890651622</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706454246471721</v>
+        <v>4.70659409538582</v>
       </c>
       <c r="K11" t="n">
-        <v>20.55392821738323</v>
+        <v>18.33555069086971</v>
       </c>
       <c r="L11" t="n">
-        <v>42.58509568451231</v>
+        <v>42.60687184175757</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89021636904666</v>
+        <v>99.88956823857036</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>76.94513769584812</v>
+        <v>79.31108064983917</v>
       </c>
       <c r="C12" t="n">
-        <v>34.75917856764546</v>
+        <v>37.1072705232415</v>
       </c>
       <c r="D12" t="n">
-        <v>1.495711809163458</v>
+        <v>1.60451583647069</v>
       </c>
       <c r="E12" t="n">
-        <v>9.426492165010043</v>
+        <v>9.981215939837293</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539303292148363</v>
+        <v>0.7539310433272318</v>
       </c>
       <c r="G12" t="n">
-        <v>23.12447881261616</v>
+        <v>24.8107725770037</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68079514388246</v>
+        <v>34.68082799305265</v>
       </c>
       <c r="I12" t="n">
-        <v>2.751664878368435</v>
+        <v>2.767748239352416</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712064557592726</v>
+        <v>4.712069020795198</v>
       </c>
       <c r="K12" t="n">
-        <v>23.05486230415189</v>
+        <v>20.68891935016083</v>
       </c>
       <c r="L12" t="n">
-        <v>42.09434617247041</v>
+        <v>42.11165904630179</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90838704426776</v>
+        <v>99.90784891970412</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>74.42773645987732</v>
+        <v>76.84239781176355</v>
       </c>
       <c r="C13" t="n">
-        <v>32.66538755758489</v>
+        <v>35.06616203625112</v>
       </c>
       <c r="D13" t="n">
-        <v>1.386543278697947</v>
+        <v>1.497183538448768</v>
       </c>
       <c r="E13" t="n">
-        <v>9.121042963708344</v>
+        <v>9.6983280974463</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7547053898506603</v>
+        <v>0.7546861173604587</v>
       </c>
       <c r="G13" t="n">
-        <v>21.43667682142505</v>
+        <v>23.15108360674919</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71644793313036</v>
+        <v>34.71556139858108</v>
       </c>
       <c r="I13" t="n">
-        <v>2.295411386498348</v>
+        <v>2.308766819674867</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716908686566626</v>
+        <v>4.716788233502865</v>
       </c>
       <c r="K13" t="n">
-        <v>25.57226354012267</v>
+        <v>23.15760218823646</v>
       </c>
       <c r="L13" t="n">
-        <v>41.68591376678221</v>
+        <v>41.69935387997486</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92356486448978</v>
+        <v>99.92311810446245</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.12433780107408</v>
+        <v>83.54786215475492</v>
       </c>
       <c r="C14" t="n">
-        <v>37.40265421116322</v>
+        <v>39.13582951870473</v>
       </c>
       <c r="D14" t="n">
-        <v>1.388285043686907</v>
+        <v>1.499048545607922</v>
       </c>
       <c r="E14" t="n">
-        <v>11.74520789506153</v>
+        <v>11.99038016760046</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556534449494202</v>
+        <v>0.7556262125295851</v>
       </c>
       <c r="G14" t="n">
-        <v>23.56049275364836</v>
+        <v>24.93952519725636</v>
       </c>
       <c r="H14" t="n">
-        <v>36.85694581155695</v>
+        <v>36.51840859355809</v>
       </c>
       <c r="I14" t="n">
-        <v>3.094918821237017</v>
+        <v>3.1222096098926</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722834030933876</v>
+        <v>4.722663828309906</v>
       </c>
       <c r="K14" t="n">
-        <v>17.87566219892592</v>
+        <v>16.45213784524509</v>
       </c>
       <c r="L14" t="n">
-        <v>44.61864906038548</v>
+        <v>44.30808846325662</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89696547047463</v>
+        <v>99.89605582720644</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.38047738304331</v>
+        <v>82.76948348744283</v>
       </c>
       <c r="C15" t="n">
-        <v>37.13562855559837</v>
+        <v>38.83984167927844</v>
       </c>
       <c r="D15" t="n">
-        <v>1.361580098590061</v>
+        <v>1.470225850654585</v>
       </c>
       <c r="E15" t="n">
-        <v>11.94958238071409</v>
+        <v>12.19393230009078</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7564525580012699</v>
+        <v>0.7564188080786859</v>
       </c>
       <c r="G15" t="n">
-        <v>23.10728491401775</v>
+        <v>24.46000481804804</v>
       </c>
       <c r="H15" t="n">
-        <v>36.89592249676389</v>
+        <v>36.55671368095653</v>
       </c>
       <c r="I15" t="n">
-        <v>2.581826447448321</v>
+        <v>2.604570479122431</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727828487507936</v>
+        <v>4.727617550491786</v>
       </c>
       <c r="K15" t="n">
-        <v>18.61952261695669</v>
+        <v>17.23051651255717</v>
       </c>
       <c r="L15" t="n">
-        <v>44.15887886018835</v>
+        <v>43.84291376344515</v>
       </c>
       <c r="M15" t="n">
-        <v>99.9140300327434</v>
+        <v>99.91327195528076</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.89859955175331</v>
+        <v>80.32481389414376</v>
       </c>
       <c r="C16" t="n">
-        <v>35.05160912662319</v>
+        <v>36.79765808345114</v>
       </c>
       <c r="D16" t="n">
-        <v>1.269944242742844</v>
+        <v>1.377189696837584</v>
       </c>
       <c r="E16" t="n">
-        <v>11.50427544084592</v>
+        <v>11.78437011218015</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7571407852937903</v>
+        <v>0.7571007345550569</v>
       </c>
       <c r="G16" t="n">
-        <v>21.5521389247409</v>
+        <v>22.91217135450003</v>
       </c>
       <c r="H16" t="n">
-        <v>36.92949073653835</v>
+        <v>36.58967027944656</v>
       </c>
       <c r="I16" t="n">
-        <v>2.153479513505301</v>
+        <v>2.172432125655273</v>
       </c>
       <c r="J16" t="n">
-        <v>4.732129908086188</v>
+        <v>4.731879590969104</v>
       </c>
       <c r="K16" t="n">
-        <v>21.10140044824671</v>
+        <v>19.67518610585624</v>
       </c>
       <c r="L16" t="n">
-        <v>43.77527302381209</v>
+        <v>43.45480663071701</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92828259868199</v>
+        <v>99.9276508200244</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.95469340371147</v>
+        <v>82.05365196636831</v>
       </c>
       <c r="C17" t="n">
-        <v>36.51555161969257</v>
+        <v>38.04242871910276</v>
       </c>
       <c r="D17" t="n">
-        <v>1.271079954884827</v>
+        <v>1.378418012025833</v>
       </c>
       <c r="E17" t="n">
-        <v>12.41222479528981</v>
+        <v>12.58417839671534</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7578178968976761</v>
+        <v>0.7577759925339862</v>
       </c>
       <c r="G17" t="n">
-        <v>22.10708485935128</v>
+        <v>23.35598635165001</v>
       </c>
       <c r="H17" t="n">
-        <v>37.49818864905171</v>
+        <v>37.04568423488482</v>
       </c>
       <c r="I17" t="n">
-        <v>2.171935392625709</v>
+        <v>2.195509025220903</v>
       </c>
       <c r="J17" t="n">
-        <v>4.736361855610475</v>
+        <v>4.736099953337412</v>
       </c>
       <c r="K17" t="n">
-        <v>19.04530659628853</v>
+        <v>17.94634803363169</v>
       </c>
       <c r="L17" t="n">
-        <v>44.36680862519925</v>
+        <v>43.93810482739414</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92766684118035</v>
+        <v>99.92688158012859</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.46273302349881</v>
+        <v>79.69711386447948</v>
       </c>
       <c r="C18" t="n">
-        <v>34.35790481963119</v>
+        <v>36.0247524600948</v>
       </c>
       <c r="D18" t="n">
-        <v>1.183489085388302</v>
+        <v>1.292364683065617</v>
       </c>
       <c r="E18" t="n">
-        <v>11.85878088516292</v>
+        <v>12.1037254061501</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7584010463790217</v>
+        <v>0.7583563070508033</v>
       </c>
       <c r="G18" t="n">
-        <v>20.58367260080497</v>
+        <v>21.89789427858212</v>
       </c>
       <c r="H18" t="n">
-        <v>37.5270439312397</v>
+        <v>37.0740542922088</v>
       </c>
       <c r="I18" t="n">
-        <v>1.811338934655015</v>
+        <v>1.830991978354517</v>
       </c>
       <c r="J18" t="n">
-        <v>4.740006539868885</v>
+        <v>4.739726919067518</v>
       </c>
       <c r="K18" t="n">
-        <v>21.53726697650117</v>
+        <v>20.30288613552053</v>
       </c>
       <c r="L18" t="n">
-        <v>44.04449666518361</v>
+        <v>43.61137504257299</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93966846131597</v>
+        <v>99.93901363818831</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.53129007161762</v>
+        <v>78.76796820222621</v>
       </c>
       <c r="C19" t="n">
-        <v>33.70447551788943</v>
+        <v>35.3774994540335</v>
       </c>
       <c r="D19" t="n">
-        <v>1.151453536093756</v>
+        <v>1.259155071476905</v>
       </c>
       <c r="E19" t="n">
-        <v>11.78951694028462</v>
+        <v>12.04716738437764</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7588935405191048</v>
+        <v>0.7588462980671309</v>
       </c>
       <c r="G19" t="n">
-        <v>20.02649867634117</v>
+        <v>21.33518889585893</v>
       </c>
       <c r="H19" t="n">
-        <v>37.55141342455596</v>
+        <v>37.09800867008254</v>
       </c>
       <c r="I19" t="n">
-        <v>1.510429325578604</v>
+        <v>1.526812519443512</v>
       </c>
       <c r="J19" t="n">
-        <v>4.743084628244405</v>
+        <v>4.742789362919566</v>
       </c>
       <c r="K19" t="n">
-        <v>22.46870992838237</v>
+        <v>21.23203179777379</v>
       </c>
       <c r="L19" t="n">
-        <v>43.7764995833211</v>
+        <v>43.33960785990509</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9496850295929</v>
+        <v>99.94913911171237</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.84519890036724</v>
+        <v>76.24107723869649</v>
       </c>
       <c r="C20" t="n">
-        <v>31.25005337276307</v>
+        <v>33.08552398061802</v>
       </c>
       <c r="D20" t="n">
-        <v>1.058229749799428</v>
+        <v>1.16795695581156</v>
       </c>
       <c r="E20" t="n">
-        <v>11.04491558051706</v>
+        <v>11.38679016093447</v>
       </c>
       <c r="F20" t="n">
-        <v>0.759319196108585</v>
+        <v>0.7592686647612503</v>
       </c>
       <c r="G20" t="n">
-        <v>18.40511668019012</v>
+        <v>19.78992328978523</v>
       </c>
       <c r="H20" t="n">
-        <v>37.57247562651661</v>
+        <v>37.11865707190028</v>
       </c>
       <c r="I20" t="n">
-        <v>1.259397091556771</v>
+        <v>1.273051940745892</v>
       </c>
       <c r="J20" t="n">
-        <v>4.745744975678655</v>
+        <v>4.745429154757812</v>
       </c>
       <c r="K20" t="n">
-        <v>25.15480109963277</v>
+        <v>23.75892276130353</v>
       </c>
       <c r="L20" t="n">
-        <v>43.5531891574492</v>
+        <v>43.11314179920502</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95804362984504</v>
+        <v>99.95758854112657</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.0873667884634</v>
+        <v>82.10067768140173</v>
       </c>
       <c r="C21" t="n">
-        <v>35.10800578486182</v>
+        <v>36.65274813606306</v>
       </c>
       <c r="D21" t="n">
-        <v>1.059027542458621</v>
+        <v>1.168860844817588</v>
       </c>
       <c r="E21" t="n">
-        <v>13.12773031850871</v>
+        <v>13.33022575911918</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7598916420077433</v>
+        <v>0.7598562674081495</v>
       </c>
       <c r="G21" t="n">
-        <v>20.18782398353601</v>
+        <v>21.42217104987491</v>
       </c>
       <c r="H21" t="n">
-        <v>39.3696330795265</v>
+        <v>38.76431564467112</v>
       </c>
       <c r="I21" t="n">
-        <v>1.833937459877413</v>
+        <v>1.906146444209846</v>
       </c>
       <c r="J21" t="n">
-        <v>4.749322762548394</v>
+        <v>4.749101671300932</v>
       </c>
       <c r="K21" t="n">
-        <v>18.91263321153662</v>
+        <v>17.89932231859827</v>
       </c>
       <c r="L21" t="n">
-        <v>45.91827580667935</v>
+        <v>45.38444046511779</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93891480307778</v>
+        <v>99.93651091977912</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_81_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_81_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.69807327597362</v>
+        <v>45.55662580594798</v>
       </c>
       <c r="M2" t="n">
-        <v>98.50980771164416</v>
+        <v>99.3204281947223</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.0244074353771</v>
+        <v>88.05784576218376</v>
       </c>
       <c r="C3" t="n">
-        <v>45.933316649852</v>
+        <v>45.94222798739884</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2287196581641</v>
+        <v>2.228798655518077</v>
       </c>
       <c r="E3" t="n">
-        <v>5.708808350546555</v>
+        <v>5.71575239552566</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429065527213669</v>
+        <v>0.7429328851726924</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97476784781862</v>
+        <v>33.97750605120837</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17370142518287</v>
+        <v>34.17491271794385</v>
       </c>
       <c r="I3" t="n">
-        <v>6.552337646435045</v>
+        <v>6.574612524485786</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643165954508542</v>
+        <v>4.643330532329327</v>
       </c>
       <c r="K3" t="n">
-        <v>11.9755925646229</v>
+        <v>11.94215423781626</v>
       </c>
       <c r="L3" t="n">
-        <v>48.85589430857267</v>
+        <v>48.87963010463055</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7648035230476</v>
+        <v>106.7640123298456</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.13690795412815</v>
+        <v>87.16203364717177</v>
       </c>
       <c r="C4" t="n">
-        <v>42.67774982333991</v>
+        <v>42.68231850081362</v>
       </c>
       <c r="D4" t="n">
-        <v>2.186092422367552</v>
+        <v>2.18575228201767</v>
       </c>
       <c r="E4" t="n">
-        <v>6.511571534488525</v>
+        <v>6.520417927804819</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444615652920431</v>
+        <v>0.7444927997238641</v>
       </c>
       <c r="G4" t="n">
-        <v>33.32495510224661</v>
+        <v>33.32127431288086</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24523200343398</v>
+        <v>34.24666878729774</v>
       </c>
       <c r="I4" t="n">
-        <v>5.471710543224197</v>
+        <v>5.490347539172662</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652884783075269</v>
+        <v>4.65307999827415</v>
       </c>
       <c r="K4" t="n">
-        <v>12.86309204587184</v>
+        <v>12.83796635282824</v>
       </c>
       <c r="L4" t="n">
-        <v>44.27714875172061</v>
+        <v>44.297087020678</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81799062093236</v>
+        <v>99.81737187431985</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.0256563479786</v>
+        <v>86.08614317368885</v>
       </c>
       <c r="C5" t="n">
-        <v>42.41578881591516</v>
+        <v>42.45859511827385</v>
       </c>
       <c r="D5" t="n">
-        <v>2.132050061308528</v>
+        <v>2.133577485277874</v>
       </c>
       <c r="E5" t="n">
-        <v>7.111903950431668</v>
+        <v>7.128674490004955</v>
       </c>
       <c r="F5" t="n">
-        <v>0.745779223888684</v>
+        <v>0.7458140791175178</v>
       </c>
       <c r="G5" t="n">
-        <v>32.50112934013133</v>
+        <v>32.52588193073007</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30584429887946</v>
+        <v>34.30744763940582</v>
       </c>
       <c r="I5" t="n">
-        <v>4.567829324034644</v>
+        <v>4.583409554668138</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661120149304275</v>
+        <v>4.661337994484486</v>
       </c>
       <c r="K5" t="n">
-        <v>13.97434365202142</v>
+        <v>13.91385682631114</v>
       </c>
       <c r="L5" t="n">
-        <v>43.4578755725294</v>
+        <v>43.47503840154911</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84800804046598</v>
+        <v>99.84749034613411</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.65612676925224</v>
+        <v>84.74826150723715</v>
       </c>
       <c r="C6" t="n">
-        <v>41.75575373648312</v>
+        <v>41.83265097904928</v>
       </c>
       <c r="D6" t="n">
-        <v>2.065199323396653</v>
+        <v>2.06837655037252</v>
       </c>
       <c r="E6" t="n">
-        <v>7.524282222037945</v>
+        <v>7.54836862127898</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468986892760759</v>
+        <v>0.7469361980081499</v>
       </c>
       <c r="G6" t="n">
-        <v>31.48205173084501</v>
+        <v>31.53190916661058</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35733970669948</v>
+        <v>34.35906510837489</v>
       </c>
       <c r="I6" t="n">
-        <v>3.812238289021594</v>
+        <v>3.82525462504108</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668116807975474</v>
+        <v>4.668351237550938</v>
       </c>
       <c r="K6" t="n">
-        <v>15.34387323074777</v>
+        <v>15.25173849276285</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77348888487927</v>
+        <v>42.78829359611375</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87311585211016</v>
+        <v>99.87268306792586</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.09577970689041</v>
+        <v>83.25804376610901</v>
       </c>
       <c r="C7" t="n">
-        <v>40.78756244333577</v>
+        <v>40.93665815973112</v>
       </c>
       <c r="D7" t="n">
-        <v>1.98927550498178</v>
+        <v>1.996016719508549</v>
       </c>
       <c r="E7" t="n">
-        <v>7.777816927520489</v>
+        <v>7.816261699324119</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478517357456563</v>
+        <v>0.7478906844625368</v>
       </c>
       <c r="G7" t="n">
-        <v>30.32466340911678</v>
+        <v>30.42880073420107</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40117984430018</v>
+        <v>34.40297148527669</v>
       </c>
       <c r="I7" t="n">
-        <v>3.180918936815182</v>
+        <v>3.191785665445197</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674073348410352</v>
+        <v>4.674316777890856</v>
       </c>
       <c r="K7" t="n">
-        <v>16.90422029310957</v>
+        <v>16.741956233891</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20232175552628</v>
+        <v>42.21512853346006</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89410449197163</v>
+        <v>99.89374292708217</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.05341803707684</v>
+        <v>88.21927979411285</v>
       </c>
       <c r="C8" t="n">
-        <v>43.09547587932384</v>
+        <v>43.30709709423148</v>
       </c>
       <c r="D8" t="n">
-        <v>1.993571857100984</v>
+        <v>2.000284475353773</v>
       </c>
       <c r="E8" t="n">
-        <v>9.618732084715843</v>
+        <v>9.696071162131707</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494669139256893</v>
+        <v>0.7494897766990936</v>
       </c>
       <c r="G8" t="n">
-        <v>30.82678078843065</v>
+        <v>30.95384815729941</v>
       </c>
       <c r="H8" t="n">
-        <v>34.4754780405817</v>
+        <v>34.4765297281583</v>
       </c>
       <c r="I8" t="n">
-        <v>5.70522014028642</v>
+        <v>5.658745390101229</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684168212035559</v>
+        <v>4.684311104369336</v>
       </c>
       <c r="K8" t="n">
-        <v>11.94658196292316</v>
+        <v>11.78072020588715</v>
       </c>
       <c r="L8" t="n">
-        <v>44.76817799759034</v>
+        <v>44.72396029869707</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81023583983735</v>
+        <v>99.8117775988157</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.01535681991375</v>
+        <v>86.3074490097238</v>
       </c>
       <c r="C9" t="n">
-        <v>41.94288211316096</v>
+        <v>42.27379964683121</v>
       </c>
       <c r="D9" t="n">
-        <v>1.901337234896918</v>
+        <v>1.914106127770289</v>
       </c>
       <c r="E9" t="n">
-        <v>9.967566014410826</v>
+        <v>10.0657057428445</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508503123490543</v>
+        <v>0.7508572749058431</v>
       </c>
       <c r="G9" t="n">
-        <v>29.40054853617407</v>
+        <v>29.62026210070895</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53911436805649</v>
+        <v>34.53943464566878</v>
       </c>
       <c r="I9" t="n">
-        <v>4.763125901844809</v>
+        <v>4.724225149663906</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692814452181589</v>
+        <v>4.69285796816152</v>
       </c>
       <c r="K9" t="n">
-        <v>13.98464318008625</v>
+        <v>13.6925509902762</v>
       </c>
       <c r="L9" t="n">
-        <v>43.91399636952261</v>
+        <v>43.87646199094532</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84152166276982</v>
+        <v>99.84281262805274</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.86717572872587</v>
+        <v>84.20673679319758</v>
       </c>
       <c r="C10" t="n">
-        <v>40.53366627078812</v>
+        <v>40.90636141160115</v>
       </c>
       <c r="D10" t="n">
-        <v>1.805215654913886</v>
+        <v>1.820284726099603</v>
       </c>
       <c r="E10" t="n">
-        <v>10.12624902976471</v>
+        <v>10.22949385699737</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520367272510783</v>
+        <v>0.7520292435104587</v>
       </c>
       <c r="G10" t="n">
-        <v>27.91421190646089</v>
+        <v>28.16840189932145</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59368945354959</v>
+        <v>34.59334520148109</v>
       </c>
       <c r="I10" t="n">
-        <v>3.975543411466494</v>
+        <v>3.942999093847255</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700229545319239</v>
+        <v>4.700182771940367</v>
       </c>
       <c r="K10" t="n">
-        <v>16.13282427127411</v>
+        <v>15.7932632068024</v>
       </c>
       <c r="L10" t="n">
-        <v>43.20120040510875</v>
+        <v>43.16914690521688</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86769094717098</v>
+        <v>99.86877152362042</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.66444930913028</v>
+        <v>82.01119378561047</v>
       </c>
       <c r="C11" t="n">
-        <v>38.94714570594309</v>
+        <v>39.32230548137612</v>
       </c>
       <c r="D11" t="n">
-        <v>1.707730031246004</v>
+        <v>1.723215302284571</v>
       </c>
       <c r="E11" t="n">
-        <v>10.13231574788305</v>
+        <v>10.23236181929239</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530550552617313</v>
+        <v>0.7530349382285997</v>
       </c>
       <c r="G11" t="n">
-        <v>26.40678294666243</v>
+        <v>26.66627945498482</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64053254203962</v>
+        <v>34.63960715851557</v>
       </c>
       <c r="I11" t="n">
-        <v>3.317438890651622</v>
+        <v>3.290226748375774</v>
       </c>
       <c r="J11" t="n">
-        <v>4.70659409538582</v>
+        <v>4.706468363928748</v>
       </c>
       <c r="K11" t="n">
-        <v>18.33555069086971</v>
+        <v>17.98880621438951</v>
       </c>
       <c r="L11" t="n">
-        <v>42.60687184175757</v>
+        <v>42.57936055162751</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88956823857036</v>
+        <v>99.89047224739315</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.31108064983917</v>
+        <v>79.72076001726177</v>
       </c>
       <c r="C12" t="n">
-        <v>37.1072705232415</v>
+        <v>37.54143368371606</v>
       </c>
       <c r="D12" t="n">
-        <v>1.60451583647069</v>
+        <v>1.622882139278355</v>
       </c>
       <c r="E12" t="n">
-        <v>9.981215939837293</v>
+        <v>10.09408920990839</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539310433272318</v>
+        <v>0.7538992396014235</v>
       </c>
       <c r="G12" t="n">
-        <v>24.8107725770037</v>
+        <v>25.11365155075299</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68082799305265</v>
+        <v>34.67936502166547</v>
       </c>
       <c r="I12" t="n">
-        <v>2.767748239352416</v>
+        <v>2.745002608546246</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712069020795198</v>
+        <v>4.711870247508896</v>
       </c>
       <c r="K12" t="n">
-        <v>20.68891935016083</v>
+        <v>20.27923998273823</v>
       </c>
       <c r="L12" t="n">
-        <v>42.11165904630179</v>
+        <v>42.0879311460908</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90784891970412</v>
+        <v>99.90860481254509</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.84239781176355</v>
+        <v>77.38454311146209</v>
       </c>
       <c r="C13" t="n">
-        <v>35.06616203625112</v>
+        <v>35.62955559603957</v>
       </c>
       <c r="D13" t="n">
-        <v>1.497183538448768</v>
+        <v>1.521439635261402</v>
       </c>
       <c r="E13" t="n">
-        <v>9.6983280974463</v>
+        <v>9.844758086743751</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546861173604587</v>
+        <v>0.7546428192277108</v>
       </c>
       <c r="G13" t="n">
-        <v>23.15108360674919</v>
+        <v>23.54385690167857</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71556139858108</v>
+        <v>34.71356968447468</v>
       </c>
       <c r="I13" t="n">
-        <v>2.308766819674867</v>
+        <v>2.289758363902772</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716788233502865</v>
+        <v>4.716517620173192</v>
       </c>
       <c r="K13" t="n">
-        <v>23.15760218823646</v>
+        <v>22.61545688853791</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69935387997486</v>
+        <v>41.67873744296291</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92311810446245</v>
+        <v>99.92374992754038</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.54786215475492</v>
+        <v>84.06816880305162</v>
       </c>
       <c r="C14" t="n">
-        <v>39.13582951870473</v>
+        <v>39.81903548968829</v>
       </c>
       <c r="D14" t="n">
-        <v>1.499048545607922</v>
+        <v>1.52318274018059</v>
       </c>
       <c r="E14" t="n">
-        <v>11.99038016760046</v>
+        <v>12.17637707797104</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556262125295851</v>
+        <v>0.7555074093040692</v>
       </c>
       <c r="G14" t="n">
-        <v>24.93952519725636</v>
+        <v>25.40958870949236</v>
       </c>
       <c r="H14" t="n">
-        <v>36.51840859355809</v>
+        <v>36.59209857003403</v>
       </c>
       <c r="I14" t="n">
-        <v>3.1222096098926</v>
+        <v>2.889492987919095</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722663828309906</v>
+        <v>4.721921308150432</v>
       </c>
       <c r="K14" t="n">
-        <v>16.45213784524509</v>
+        <v>15.93183119694837</v>
       </c>
       <c r="L14" t="n">
-        <v>44.30808846325662</v>
+        <v>44.15292710335186</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89605582720644</v>
+        <v>99.90379378998851</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.76948348744283</v>
+        <v>83.41748605963092</v>
       </c>
       <c r="C15" t="n">
-        <v>38.83984167927844</v>
+        <v>39.58147045566038</v>
       </c>
       <c r="D15" t="n">
-        <v>1.470225850654585</v>
+        <v>1.49532771331109</v>
       </c>
       <c r="E15" t="n">
-        <v>12.19393230009078</v>
+        <v>12.38926177144577</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7564188080786859</v>
+        <v>0.7562350531332742</v>
       </c>
       <c r="G15" t="n">
-        <v>24.46000481804804</v>
+        <v>24.97876759913727</v>
       </c>
       <c r="H15" t="n">
-        <v>36.55671368095653</v>
+        <v>36.66119491167043</v>
       </c>
       <c r="I15" t="n">
-        <v>2.604570479122431</v>
+        <v>2.410229928850117</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727617550491786</v>
+        <v>4.726469082082963</v>
       </c>
       <c r="K15" t="n">
-        <v>17.23051651255717</v>
+        <v>16.58251394036906</v>
       </c>
       <c r="L15" t="n">
-        <v>43.84291376344515</v>
+        <v>43.75575190986169</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91327195528076</v>
+        <v>99.91973630589113</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.32481389414376</v>
+        <v>81.0221591059473</v>
       </c>
       <c r="C16" t="n">
-        <v>36.79765808345114</v>
+        <v>37.55901934012853</v>
       </c>
       <c r="D16" t="n">
-        <v>1.377189696837584</v>
+        <v>1.404324239261067</v>
       </c>
       <c r="E16" t="n">
-        <v>11.78437011218015</v>
+        <v>11.97030028607977</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7571007345550569</v>
+        <v>0.7568604676876636</v>
       </c>
       <c r="G16" t="n">
-        <v>22.91217135450003</v>
+        <v>23.45859606163783</v>
       </c>
       <c r="H16" t="n">
-        <v>36.58967027944656</v>
+        <v>36.69151411571163</v>
       </c>
       <c r="I16" t="n">
-        <v>2.172432125655273</v>
+        <v>2.010186012521445</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731879590969104</v>
+        <v>4.730377923047897</v>
       </c>
       <c r="K16" t="n">
-        <v>19.67518610585624</v>
+        <v>18.97784089405269</v>
       </c>
       <c r="L16" t="n">
-        <v>43.45480663071701</v>
+        <v>43.39618893446183</v>
       </c>
       <c r="M16" t="n">
-        <v>99.9276508200244</v>
+        <v>99.93304916864304</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.05365196636831</v>
+        <v>82.80762438575283</v>
       </c>
       <c r="C17" t="n">
-        <v>38.04242871910276</v>
+        <v>38.86248671029935</v>
       </c>
       <c r="D17" t="n">
-        <v>1.378418012025833</v>
+        <v>1.405448019406195</v>
       </c>
       <c r="E17" t="n">
-        <v>12.58417839671534</v>
+        <v>12.78225372858584</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7577759925339862</v>
+        <v>0.757466128932012</v>
       </c>
       <c r="G17" t="n">
-        <v>23.35598635165001</v>
+        <v>23.94841769910329</v>
       </c>
       <c r="H17" t="n">
-        <v>37.04568423488482</v>
+        <v>37.19192511007596</v>
       </c>
       <c r="I17" t="n">
-        <v>2.195509025220903</v>
+        <v>1.987950393824462</v>
       </c>
       <c r="J17" t="n">
-        <v>4.736099953337412</v>
+        <v>4.734163305825074</v>
       </c>
       <c r="K17" t="n">
-        <v>17.94634803363169</v>
+        <v>17.19237561424719</v>
       </c>
       <c r="L17" t="n">
-        <v>43.93810482739414</v>
+        <v>43.87892564707179</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92688158012859</v>
+        <v>99.93378797161832</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.69711386447948</v>
+        <v>80.4126017738575</v>
       </c>
       <c r="C18" t="n">
-        <v>36.0247524600948</v>
+        <v>36.77466718549654</v>
       </c>
       <c r="D18" t="n">
-        <v>1.292364683065617</v>
+        <v>1.318088301182066</v>
       </c>
       <c r="E18" t="n">
-        <v>12.1037254061501</v>
+        <v>12.26402944818773</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7583563070508033</v>
+        <v>0.7579866526059281</v>
       </c>
       <c r="G18" t="n">
-        <v>21.89789427858212</v>
+        <v>22.45983399254164</v>
       </c>
       <c r="H18" t="n">
-        <v>37.0740542922088</v>
+        <v>37.21748305485905</v>
       </c>
       <c r="I18" t="n">
-        <v>1.830991978354517</v>
+        <v>1.657763745694044</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739726919067518</v>
+        <v>4.73741657878705</v>
       </c>
       <c r="K18" t="n">
-        <v>20.30288613552053</v>
+        <v>19.58739822614249</v>
       </c>
       <c r="L18" t="n">
-        <v>43.61137504257299</v>
+        <v>43.58271374408808</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93901363818831</v>
+        <v>99.94477915572712</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.76796820222621</v>
+        <v>79.42690744383962</v>
       </c>
       <c r="C19" t="n">
-        <v>35.3774994540335</v>
+        <v>36.04448902917921</v>
       </c>
       <c r="D19" t="n">
-        <v>1.259155071476905</v>
+        <v>1.282784240482048</v>
       </c>
       <c r="E19" t="n">
-        <v>12.04716738437764</v>
+        <v>12.16592464413313</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7588462980671309</v>
+        <v>0.758426362161765</v>
       </c>
       <c r="G19" t="n">
-        <v>21.33518889585893</v>
+        <v>21.85826326175378</v>
       </c>
       <c r="H19" t="n">
-        <v>37.09800867008254</v>
+        <v>37.23907299036406</v>
       </c>
       <c r="I19" t="n">
-        <v>1.526812519443512</v>
+        <v>1.38227118143382</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742789362919566</v>
+        <v>4.74016476351103</v>
       </c>
       <c r="K19" t="n">
-        <v>21.23203179777379</v>
+        <v>20.57309255616038</v>
       </c>
       <c r="L19" t="n">
-        <v>43.33960785990509</v>
+        <v>43.33636942172447</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94913911171237</v>
+        <v>99.95395100706405</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.24107723869649</v>
+        <v>76.86895398294753</v>
       </c>
       <c r="C20" t="n">
-        <v>33.08552398061802</v>
+        <v>33.69942715617109</v>
       </c>
       <c r="D20" t="n">
-        <v>1.16795695581156</v>
+        <v>1.190442486500163</v>
       </c>
       <c r="E20" t="n">
-        <v>11.38679016093447</v>
+        <v>11.48223358048729</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7592686647612503</v>
+        <v>0.7588053891968307</v>
       </c>
       <c r="G20" t="n">
-        <v>19.78992328978523</v>
+        <v>20.28478714247307</v>
       </c>
       <c r="H20" t="n">
-        <v>37.11865707190028</v>
+        <v>37.25768338700679</v>
       </c>
       <c r="I20" t="n">
-        <v>1.273051940745892</v>
+        <v>1.152468314803182</v>
       </c>
       <c r="J20" t="n">
-        <v>4.745429154757812</v>
+        <v>4.74253368248019</v>
       </c>
       <c r="K20" t="n">
-        <v>23.75892276130353</v>
+        <v>23.13104601705248</v>
       </c>
       <c r="L20" t="n">
-        <v>43.11314179920502</v>
+        <v>43.13113040506994</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95758854112657</v>
+        <v>99.96160357829351</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.10067768140173</v>
+        <v>82.7444391035075</v>
       </c>
       <c r="C21" t="n">
-        <v>36.65274813606306</v>
+        <v>37.33802486223179</v>
       </c>
       <c r="D21" t="n">
-        <v>1.168860844817588</v>
+        <v>1.191248358724532</v>
       </c>
       <c r="E21" t="n">
-        <v>13.33022575911918</v>
+        <v>13.44214550811311</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7598562674081495</v>
+        <v>0.7593190638966083</v>
       </c>
       <c r="G21" t="n">
-        <v>21.42217104987491</v>
+        <v>21.97058797590163</v>
       </c>
       <c r="H21" t="n">
-        <v>38.76431564467112</v>
+        <v>38.95497405367441</v>
       </c>
       <c r="I21" t="n">
-        <v>1.906146444209846</v>
+        <v>1.680419993843432</v>
       </c>
       <c r="J21" t="n">
-        <v>4.749101671300932</v>
+        <v>4.745744149353801</v>
       </c>
       <c r="K21" t="n">
-        <v>17.89932231859827</v>
+        <v>17.25556089649251</v>
       </c>
       <c r="L21" t="n">
-        <v>45.38444046511779</v>
+        <v>45.35043813460899</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93651091977912</v>
+        <v>99.94402389333328</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_81_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_81_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.55662580594798</v>
+        <v>43.865012703683</v>
       </c>
       <c r="M2" t="n">
-        <v>99.3204281947223</v>
+        <v>94.14057121188895</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.05784576218376</v>
+        <v>81.31796519293941</v>
       </c>
       <c r="C3" t="n">
-        <v>45.94222798739884</v>
+        <v>43.07352074849498</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228798655518077</v>
+        <v>2.171848857752495</v>
       </c>
       <c r="E3" t="n">
-        <v>5.71575239552566</v>
+        <v>4.131915181223554</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429328851726924</v>
+        <v>0.7375206023559288</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97750605120837</v>
+        <v>32.66822656869378</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17491271794385</v>
+        <v>33.92594770837272</v>
       </c>
       <c r="I3" t="n">
-        <v>6.574612524485786</v>
+        <v>3.07300250981637</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643330532329327</v>
+        <v>4.609503764724555</v>
       </c>
       <c r="K3" t="n">
-        <v>11.94215423781626</v>
+        <v>18.68203480706059</v>
       </c>
       <c r="L3" t="n">
-        <v>48.87963010463055</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7640123298456</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.16203364717177</v>
+        <v>88.20032105965716</v>
       </c>
       <c r="C4" t="n">
-        <v>42.68231850081362</v>
+        <v>42.66480307825456</v>
       </c>
       <c r="D4" t="n">
-        <v>2.18575228201767</v>
+        <v>2.177423451232226</v>
       </c>
       <c r="E4" t="n">
-        <v>6.520417927804819</v>
+        <v>6.495086003631995</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444927997238641</v>
+        <v>0.7394136335060408</v>
       </c>
       <c r="G4" t="n">
-        <v>33.32127431288086</v>
+        <v>33.36238988151652</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24666878729774</v>
+        <v>34.01302714127787</v>
       </c>
       <c r="I4" t="n">
-        <v>5.490347539172662</v>
+        <v>6.79164573907976</v>
       </c>
       <c r="J4" t="n">
-        <v>4.65307999827415</v>
+        <v>4.621335209412755</v>
       </c>
       <c r="K4" t="n">
-        <v>12.83796635282824</v>
+        <v>11.79967894034283</v>
       </c>
       <c r="L4" t="n">
-        <v>44.297087020678</v>
+        <v>45.3097093843605</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81737187431985</v>
+        <v>99.77419140295788</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.08614317368885</v>
+        <v>86.62098348772211</v>
       </c>
       <c r="C5" t="n">
-        <v>42.45859511827385</v>
+        <v>42.13825952837948</v>
       </c>
       <c r="D5" t="n">
-        <v>2.133577485277874</v>
+        <v>2.10018729521986</v>
       </c>
       <c r="E5" t="n">
-        <v>7.128674490004955</v>
+        <v>7.210039562271993</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458140791175178</v>
+        <v>0.7410275600847818</v>
       </c>
       <c r="G5" t="n">
-        <v>32.52588193073007</v>
+        <v>32.17898077091107</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30744763940582</v>
+        <v>34.08726776389996</v>
       </c>
       <c r="I5" t="n">
-        <v>4.583409554668138</v>
+        <v>5.672058284804583</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661337994484486</v>
+        <v>4.631422250529885</v>
       </c>
       <c r="K5" t="n">
-        <v>13.91385682631114</v>
+        <v>13.37901651227787</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47503840154911</v>
+        <v>44.29406713325709</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84749034613411</v>
+        <v>99.81134317391445</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.74826150723715</v>
+        <v>84.79821623790517</v>
       </c>
       <c r="C6" t="n">
-        <v>41.83265097904928</v>
+        <v>41.19525381156025</v>
       </c>
       <c r="D6" t="n">
-        <v>2.06837655037252</v>
+        <v>2.011656365730706</v>
       </c>
       <c r="E6" t="n">
-        <v>7.54836862127898</v>
+        <v>7.695361133360053</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469361980081499</v>
+        <v>0.7424069705234926</v>
       </c>
       <c r="G6" t="n">
-        <v>31.53190916661058</v>
+        <v>30.82251361955439</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35906510837489</v>
+        <v>34.15072064408066</v>
       </c>
       <c r="I6" t="n">
-        <v>3.82525462504108</v>
+        <v>4.73551393888403</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668351237550938</v>
+        <v>4.640043565771828</v>
       </c>
       <c r="K6" t="n">
-        <v>15.25173849276285</v>
+        <v>15.20178376209485</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78829359611375</v>
+        <v>43.445405251767</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87268306792586</v>
+        <v>99.8424428254221</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.25804376610901</v>
+        <v>82.72819386506121</v>
       </c>
       <c r="C7" t="n">
-        <v>40.93665815973112</v>
+        <v>39.85962598561415</v>
       </c>
       <c r="D7" t="n">
-        <v>1.996016719508549</v>
+        <v>1.911952281522719</v>
       </c>
       <c r="E7" t="n">
-        <v>7.816261699324119</v>
+        <v>7.972712301037087</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478906844625368</v>
+        <v>0.7435893155164142</v>
       </c>
       <c r="G7" t="n">
-        <v>30.42880073420107</v>
+        <v>29.29485186490396</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40297148527669</v>
+        <v>34.20510851375505</v>
       </c>
       <c r="I7" t="n">
-        <v>3.191785665445197</v>
+        <v>3.952546366348388</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674316777890856</v>
+        <v>4.647433221977588</v>
       </c>
       <c r="K7" t="n">
-        <v>16.741956233891</v>
+        <v>17.27180613493879</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21512853346006</v>
+        <v>42.73702582558918</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89374292708217</v>
+        <v>99.86845794614212</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.21927979411285</v>
+        <v>80.61943784939098</v>
       </c>
       <c r="C8" t="n">
-        <v>43.30709709423148</v>
+        <v>38.36331452041389</v>
       </c>
       <c r="D8" t="n">
-        <v>2.000284475353773</v>
+        <v>1.811512464164758</v>
       </c>
       <c r="E8" t="n">
-        <v>9.696071162131707</v>
+        <v>8.10359843395201</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494897766990936</v>
+        <v>0.7446033662935814</v>
       </c>
       <c r="G8" t="n">
-        <v>30.95384815729941</v>
+        <v>27.75591723809617</v>
       </c>
       <c r="H8" t="n">
-        <v>34.4765297281583</v>
+        <v>34.25175484950474</v>
       </c>
       <c r="I8" t="n">
-        <v>5.658745390101229</v>
+        <v>3.298280458044839</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684311104369336</v>
+        <v>4.653771039334883</v>
       </c>
       <c r="K8" t="n">
-        <v>11.78072020588715</v>
+        <v>19.38056215060902</v>
       </c>
       <c r="L8" t="n">
-        <v>44.72396029869707</v>
+        <v>42.1463303743563</v>
       </c>
       <c r="M8" t="n">
-        <v>99.8117775988157</v>
+        <v>99.89020704537921</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.3074490097238</v>
+        <v>78.35585851647225</v>
       </c>
       <c r="C9" t="n">
-        <v>42.27379964683121</v>
+        <v>36.61014667764955</v>
       </c>
       <c r="D9" t="n">
-        <v>1.914106127770289</v>
+        <v>1.704655375350602</v>
       </c>
       <c r="E9" t="n">
-        <v>10.0657057428445</v>
+        <v>8.084215966340841</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508572749058431</v>
+        <v>0.7454750254688625</v>
       </c>
       <c r="G9" t="n">
-        <v>29.62026210070895</v>
+        <v>26.11865744987985</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53943464566878</v>
+        <v>34.29185117156767</v>
       </c>
       <c r="I9" t="n">
-        <v>4.724225149663906</v>
+        <v>2.751784618684024</v>
       </c>
       <c r="J9" t="n">
-        <v>4.69285796816152</v>
+        <v>4.65921890918039</v>
       </c>
       <c r="K9" t="n">
-        <v>13.6925509902762</v>
+        <v>21.64414148352776</v>
       </c>
       <c r="L9" t="n">
-        <v>43.87646199094532</v>
+        <v>41.65409293721033</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84281262805274</v>
+        <v>99.90838109838764</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.20673679319758</v>
+        <v>84.34405954289909</v>
       </c>
       <c r="C10" t="n">
-        <v>40.90636141160115</v>
+        <v>40.62176826339945</v>
       </c>
       <c r="D10" t="n">
-        <v>1.820284726099603</v>
+        <v>1.706633952080278</v>
       </c>
       <c r="E10" t="n">
-        <v>10.22949385699737</v>
+        <v>10.32502801348606</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520292435104587</v>
+        <v>0.7463402909995236</v>
       </c>
       <c r="G10" t="n">
-        <v>28.16840189932145</v>
+        <v>27.89091529376069</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59334520148109</v>
+        <v>36.07359556102172</v>
       </c>
       <c r="I10" t="n">
-        <v>3.942999093847255</v>
+        <v>2.936919612803785</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700182771940367</v>
+        <v>4.664626818747022</v>
       </c>
       <c r="K10" t="n">
-        <v>15.7932632068024</v>
+        <v>15.65594045710093</v>
       </c>
       <c r="L10" t="n">
-        <v>43.16914690521688</v>
+        <v>43.62450745579535</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86877152362042</v>
+        <v>99.90221617629571</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.01119378561047</v>
+        <v>83.73248962801557</v>
       </c>
       <c r="C11" t="n">
-        <v>39.32230548137612</v>
+        <v>40.32836505503357</v>
       </c>
       <c r="D11" t="n">
-        <v>1.723215302284571</v>
+        <v>1.669798673949336</v>
       </c>
       <c r="E11" t="n">
-        <v>10.23236181929239</v>
+        <v>10.59203456809919</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530349382285997</v>
+        <v>0.7470872030289223</v>
       </c>
       <c r="G11" t="n">
-        <v>26.66627945498482</v>
+        <v>27.359803868794</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63960715851557</v>
+        <v>36.18057129328848</v>
       </c>
       <c r="I11" t="n">
-        <v>3.290226748375774</v>
+        <v>2.513899001924882</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706468363928748</v>
+        <v>4.669295018930764</v>
       </c>
       <c r="K11" t="n">
-        <v>17.98880621438951</v>
+        <v>16.26751037198444</v>
       </c>
       <c r="L11" t="n">
-        <v>42.57936055162751</v>
+        <v>43.32041171656965</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89047224739315</v>
+        <v>99.91628714358765</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.72076001726177</v>
+        <v>81.37948581786203</v>
       </c>
       <c r="C12" t="n">
-        <v>37.54143368371606</v>
+        <v>38.36487314287413</v>
       </c>
       <c r="D12" t="n">
-        <v>1.622882139278355</v>
+        <v>1.571983503527113</v>
       </c>
       <c r="E12" t="n">
-        <v>10.09408920990839</v>
+        <v>10.32101605924503</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538992396014235</v>
+        <v>0.7477288180196314</v>
       </c>
       <c r="G12" t="n">
-        <v>25.11365155075299</v>
+        <v>25.75709336249383</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67936502166547</v>
+        <v>36.21164396702734</v>
       </c>
       <c r="I12" t="n">
-        <v>2.745002608546246</v>
+        <v>2.096714994926383</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711870247508896</v>
+        <v>4.673305112622696</v>
       </c>
       <c r="K12" t="n">
-        <v>20.27923998273823</v>
+        <v>18.62051418213798</v>
       </c>
       <c r="L12" t="n">
-        <v>42.0879311460908</v>
+        <v>42.94478214715664</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90860481254509</v>
+        <v>99.93016947216876</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.38454311146209</v>
+        <v>82.67696358379462</v>
       </c>
       <c r="C13" t="n">
-        <v>35.62955559603957</v>
+        <v>39.41832044156269</v>
       </c>
       <c r="D13" t="n">
-        <v>1.521439635261402</v>
+        <v>1.57322767061961</v>
       </c>
       <c r="E13" t="n">
-        <v>9.844758086743751</v>
+        <v>11.00342739155984</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546428192277108</v>
+        <v>0.7483206178619356</v>
       </c>
       <c r="G13" t="n">
-        <v>23.54385690167857</v>
+        <v>26.12454291151771</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71356968447468</v>
+        <v>36.58736790811692</v>
       </c>
       <c r="I13" t="n">
-        <v>2.289758363902772</v>
+        <v>1.963073222481496</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716517620173192</v>
+        <v>4.677003861637097</v>
       </c>
       <c r="K13" t="n">
-        <v>22.61545688853791</v>
+        <v>17.32303641620539</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67873744296291</v>
+        <v>43.19325911719881</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92374992754038</v>
+        <v>99.93461597496689</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.06816880305162</v>
+        <v>80.31553637833863</v>
       </c>
       <c r="C14" t="n">
-        <v>39.81903548968829</v>
+        <v>37.3607404447811</v>
       </c>
       <c r="D14" t="n">
-        <v>1.52318274018059</v>
+        <v>1.478237833776221</v>
       </c>
       <c r="E14" t="n">
-        <v>12.17637707797104</v>
+        <v>10.61188628349692</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555074093040692</v>
+        <v>0.7488290314011554</v>
       </c>
       <c r="G14" t="n">
-        <v>25.40958870949236</v>
+        <v>24.54717040840388</v>
       </c>
       <c r="H14" t="n">
-        <v>36.59209857003403</v>
+        <v>36.61222558645011</v>
       </c>
       <c r="I14" t="n">
-        <v>2.889492987919095</v>
+        <v>1.63700578855312</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721921308150432</v>
+        <v>4.680181446257221</v>
       </c>
       <c r="K14" t="n">
-        <v>15.93183119694837</v>
+        <v>19.68446362166137</v>
       </c>
       <c r="L14" t="n">
-        <v>44.15292710335186</v>
+        <v>42.90026612182194</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90379378998851</v>
+        <v>99.94547018826441</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.41748605963092</v>
+        <v>79.291063014003</v>
       </c>
       <c r="C15" t="n">
-        <v>39.58147045566038</v>
+        <v>36.53880280314723</v>
       </c>
       <c r="D15" t="n">
-        <v>1.49532771331109</v>
+        <v>1.434354264962924</v>
       </c>
       <c r="E15" t="n">
-        <v>12.38926177144577</v>
+        <v>10.54421314122976</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562350531332742</v>
+        <v>0.7492697624032436</v>
       </c>
       <c r="G15" t="n">
-        <v>24.97876759913727</v>
+        <v>23.8324709214716</v>
       </c>
       <c r="H15" t="n">
-        <v>36.66119491167043</v>
+        <v>36.64779187229994</v>
       </c>
       <c r="I15" t="n">
-        <v>2.410229928850117</v>
+        <v>1.40002703661525</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726469082082963</v>
+        <v>4.682936015020272</v>
       </c>
       <c r="K15" t="n">
-        <v>16.58251394036906</v>
+        <v>20.70893698599701</v>
       </c>
       <c r="L15" t="n">
-        <v>43.75575190986169</v>
+        <v>42.70562009348775</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91973630589113</v>
+        <v>99.95335988263199</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.0221591059473</v>
+        <v>76.61900101744627</v>
       </c>
       <c r="C16" t="n">
-        <v>37.55901934012853</v>
+        <v>34.08269429304072</v>
       </c>
       <c r="D16" t="n">
-        <v>1.404324239261067</v>
+        <v>1.328003122331421</v>
       </c>
       <c r="E16" t="n">
-        <v>11.97030028607977</v>
+        <v>9.956952452238465</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568604676876636</v>
+        <v>0.7496502636943509</v>
       </c>
       <c r="G16" t="n">
-        <v>23.45859606163783</v>
+        <v>22.06539665248263</v>
       </c>
       <c r="H16" t="n">
-        <v>36.69151411571163</v>
+        <v>36.6664027022351</v>
       </c>
       <c r="I16" t="n">
-        <v>2.010186012521445</v>
+        <v>1.167281676374617</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730377923047897</v>
+        <v>4.685314148089692</v>
       </c>
       <c r="K16" t="n">
-        <v>18.97784089405269</v>
+        <v>23.38099898255372</v>
       </c>
       <c r="L16" t="n">
-        <v>43.39618893446183</v>
+        <v>42.49741708449959</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93304916864304</v>
+        <v>99.96111036009403</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.80762438575283</v>
+        <v>82.43727969927978</v>
       </c>
       <c r="C17" t="n">
-        <v>38.86248671029935</v>
+        <v>37.92485409720319</v>
       </c>
       <c r="D17" t="n">
-        <v>1.405448019406195</v>
+        <v>1.328709073117906</v>
       </c>
       <c r="E17" t="n">
-        <v>12.78225372858584</v>
+        <v>11.98524458923156</v>
       </c>
       <c r="F17" t="n">
-        <v>0.757466128932012</v>
+        <v>0.7500487689270151</v>
       </c>
       <c r="G17" t="n">
-        <v>23.94841769910329</v>
+        <v>23.88101207076841</v>
       </c>
       <c r="H17" t="n">
-        <v>37.19192511007596</v>
+        <v>38.48977984301306</v>
       </c>
       <c r="I17" t="n">
-        <v>1.987950393824462</v>
+        <v>1.314680548427988</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734163305825074</v>
+        <v>4.687804805793843</v>
       </c>
       <c r="K17" t="n">
-        <v>17.19237561424719</v>
+        <v>17.56272030072022</v>
       </c>
       <c r="L17" t="n">
-        <v>43.87892564707179</v>
+        <v>44.468626200374</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93378797161832</v>
+        <v>99.95620059829741</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.4126017738575</v>
+        <v>84.25345404727413</v>
       </c>
       <c r="C18" t="n">
-        <v>36.77466718549654</v>
+        <v>38.69281392507955</v>
       </c>
       <c r="D18" t="n">
-        <v>1.318088301182066</v>
+        <v>1.32992249291246</v>
       </c>
       <c r="E18" t="n">
-        <v>12.26402944818773</v>
+        <v>12.62341639092284</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579866526059281</v>
+        <v>0.7507337375491993</v>
       </c>
       <c r="G18" t="n">
-        <v>22.45983399254164</v>
+        <v>24.02407682391809</v>
       </c>
       <c r="H18" t="n">
-        <v>37.21748305485905</v>
+        <v>38.52492994599231</v>
       </c>
       <c r="I18" t="n">
-        <v>1.657763745694044</v>
+        <v>2.308288796296744</v>
       </c>
       <c r="J18" t="n">
-        <v>4.73741657878705</v>
+        <v>4.692085859682494</v>
       </c>
       <c r="K18" t="n">
-        <v>19.58739822614249</v>
+        <v>15.74654595272587</v>
       </c>
       <c r="L18" t="n">
-        <v>43.58271374408808</v>
+        <v>45.48376736498853</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94477915572712</v>
+        <v>99.92312724279394</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.42690744383962</v>
+        <v>81.29111870700277</v>
       </c>
       <c r="C19" t="n">
-        <v>36.04448902917921</v>
+        <v>36.08640977118354</v>
       </c>
       <c r="D19" t="n">
-        <v>1.282784240482048</v>
+        <v>1.227153073128388</v>
       </c>
       <c r="E19" t="n">
-        <v>12.16592464413313</v>
+        <v>11.96879386327144</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758426362161765</v>
+        <v>0.7513263532655389</v>
       </c>
       <c r="G19" t="n">
-        <v>21.85826326175378</v>
+        <v>22.16762244465937</v>
       </c>
       <c r="H19" t="n">
-        <v>37.23907299036406</v>
+        <v>38.55534083312175</v>
       </c>
       <c r="I19" t="n">
-        <v>1.38227118143382</v>
+        <v>1.925092431646665</v>
       </c>
       <c r="J19" t="n">
-        <v>4.74016476351103</v>
+        <v>4.695789707909617</v>
       </c>
       <c r="K19" t="n">
-        <v>20.57309255616038</v>
+        <v>18.70888129299724</v>
       </c>
       <c r="L19" t="n">
-        <v>43.33636942172447</v>
+        <v>45.14058980258875</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95395100706405</v>
+        <v>99.93588086676952</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.86895398294753</v>
+        <v>78.28974907801056</v>
       </c>
       <c r="C20" t="n">
-        <v>33.69942715617109</v>
+        <v>33.38090005417233</v>
       </c>
       <c r="D20" t="n">
-        <v>1.190442486500163</v>
+        <v>1.123769964832561</v>
       </c>
       <c r="E20" t="n">
-        <v>11.48223358048729</v>
+        <v>11.22802394184326</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7588053891968307</v>
+        <v>0.7518398876733761</v>
       </c>
       <c r="G20" t="n">
-        <v>20.28478714247307</v>
+        <v>20.3000822314284</v>
       </c>
       <c r="H20" t="n">
-        <v>37.25768338700679</v>
+        <v>38.58169355459578</v>
       </c>
       <c r="I20" t="n">
-        <v>1.152468314803182</v>
+        <v>1.60534019967858</v>
       </c>
       <c r="J20" t="n">
-        <v>4.74253368248019</v>
+        <v>4.6989992979586</v>
       </c>
       <c r="K20" t="n">
-        <v>23.13104601705248</v>
+        <v>21.71025092198946</v>
       </c>
       <c r="L20" t="n">
-        <v>43.13113040506994</v>
+        <v>44.85537423407026</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96160357829351</v>
+        <v>99.94652521023204</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.7444391035075</v>
+        <v>75.40139824473121</v>
       </c>
       <c r="C21" t="n">
-        <v>37.33802486223179</v>
+        <v>30.7383291091203</v>
       </c>
       <c r="D21" t="n">
-        <v>1.191248358724532</v>
+        <v>1.024968620212546</v>
       </c>
       <c r="E21" t="n">
-        <v>13.44214550811311</v>
+        <v>10.46395703604453</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7593190638966083</v>
+        <v>0.7522847928548042</v>
       </c>
       <c r="G21" t="n">
-        <v>21.97058797590163</v>
+        <v>18.51530822684746</v>
       </c>
       <c r="H21" t="n">
-        <v>38.95497405367441</v>
+        <v>38.60452447332214</v>
       </c>
       <c r="I21" t="n">
-        <v>1.680419993843432</v>
+        <v>1.338575140107206</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745744149353801</v>
+        <v>4.701779955342525</v>
       </c>
       <c r="K21" t="n">
-        <v>17.25556089649251</v>
+        <v>24.59860175526878</v>
       </c>
       <c r="L21" t="n">
-        <v>45.35043813460899</v>
+        <v>44.61847635228653</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94402389333328</v>
+        <v>99.95540721667561</v>
       </c>
     </row>
   </sheetData>
